--- a/data_extactor/batch_10_fa/batch_0045_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0045_fa.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Certified Registered Nurse Anesthetist (CRNA) | Nurse Anesthetist | Staff Certified Registered Nurse Anesthetist (Staff CRNA) | Staff Nurse Anesthetist</t>
+          <t>پرستار بیهوشی دارای پروانه و گواهی صلاحیت (CRNA) | پرستار بیهوشی | پرستار بیهوشی دارای گواهی صلاحیت کادر درمان (Staff CRNA) | پرستار بیهوشی کادر درمان</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -508,27 +508,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | پایش | یادگیری فعال | سخنوری | گوش دادن فعال | علوم | راهبردهای یادگیری | نوشتن | ریاضیات</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال | سخن گفتن | گوش دادن فعال | علوم | راهبردهای یادگیری | نگارش | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | خدمات مشتری و شخصی | زیست‌شناسی | شیمی | آموزش و پرورش | ریاضیات | زبان انگلیسی | روان‌شناسی | فیزیک | رایانه و الکترونیک | مدیریت و اداره | قانون و دولت | ایمنی و امنیت عمومی | پرسنل و منابع انسانی | مهندسی و فناوری | درمان و مشاوره</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | زیست‌شناسی | شیمی | آموزش و پرورش | ریاضیات | زبان انگلیسی | روان‌شناسی | فیزیک | رایانه و الکترونیک | مدیریت و اداره | قانون و دولت | ایمنی و امنیت عمومی | پرسنل و منابع انسانی | مهندسی و فناوری | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شنیداری | درک نوشتاری | نظم‌دهی اطلاعات | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | دید نزدیک | وضوح گفتار | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | سرعت ادراکی | سرعت بستار | انعطاف‌پذیری بستار | ثبات دست و بازو | توانایی عددی | استدلال ریاضی | اصالت | مهارت انگشتان | مهارت دستی | اشتراک زمانی | تجسم | تشخیص رنگ بصری | دید دور | دقت کنترل | حافظه</t>
+          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | ترتیب‌دهی اطلاعات | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | سرعت ادراکی | سرعت بستار | انعطاف‌پذیری بستار | ثبات دست و بازو | توانایی عددی | استدلال ریاضی | اصالت | مهارت انگشتان | مهارت دستی | تقسیم توجه | تجسم | تشخیص رنگ بصری | بینایی دور | دقت کنترل | حفظ کردن</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>بحث‌های رودررو با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | در معرض بیماری یا عفونت | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا صحیح بودن | پیامد خطا | آزادی در تصمیم‌گیری | در معرض آلاینده‌ها | تماس با دیگران | نزدیکی فیزیکی | سطح رقابت | سلامت و ایمنی سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | مکالمات تلفنی | تکرار تصمیم‌گیری | اهمیت تکرار وظایف مشابه | فشار زمانی | صرف زمان برای استفاده از دست‌ها جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ایمیل | پوشیدن تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، مهار ایمنی، لباس‌های محافظ کامل یا محافظ تابش | برخورد با مشتریان خارجی یا عموم مردم | در معرض تابش | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | موقعیت‌های تعارض | نتایج کاری و خروجی‌های سایر کارکنان</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | پیامد خطا | آزادی در تصمیم‌گیری | قرار گرفتن در معرض آلاینده‌ها | ارتباط با دیگران | نزدیکی فیزیکی | سطح رقابت | سلامت و ایمنی سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | مکالمات تلفنی | فراوانی تصمیم‌گیری | اهمیت تکرار وظایف یکسان | فشار زمانی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ایمیل | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | تعامل با مشتریان خارجی یا عموم مردم | قرار گرفتن در معرض تابش | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | موقعیت‌های تعارض | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان قلب | پرستاران بالینی متخصص | پرستاران مراقبت‌های ویژه | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | پزشکان داخلی عمومی | پرستاران عملی و حرفه‌ای دارای مجوز | ماماها | پرستاران متخصص | جراحان ارتوپد، به جز کودکان | پیراپزشکان | جراحان کودکان | دستیاران پزشک | پرستاران ثبت‌نام شده | درمانگران تنفسی | دستیاران جراحی | تکنسین‌های جراحی</t>
+          <t>پرستاران مراقبت‌های ویژه | دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان قلب | متخصصان پرستاری بالینی | پرستاران بخش مراقبت‌های ویژه | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | پزشکان داخلی عمومی | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | ماماها | پرستاران متخصص | جراحان ارتوپد، به‌جز کودکان | پارامدیک‌ها | جراحان کودکان | دستیاران پزشک | پرستاران ثبت‌شده | درمانگران تنفسی | دستیاران جراحی | تکنولوژیست‌های جراحی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -550,12 +550,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ماماها (Nurse Midwives)</t>
+          <t>ماماهای پرستار (Nurse Midwives)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Certified Nurse-Midwife (CNM) | Nurse Midwife | Staff Certified Nurse Midwife | Staff Nurse Midwife</t>
+          <t>پرستار-ماما دارای گواهی صلاحیت (CNM) | پرستار-ماما | پرستار-مامای دارای گواهی صلاحیت کادر درمان | پرستار-مامای کادر درمان</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخنوری | تفکر انتقادی | درک مطلب | پایش | یادگیری فعال | نوشتن | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | روان‌شناسی | خدمات مشتری و شخصی | زبان انگلیسی | زیست‌شناسی | جامعه‌شناسی و مردم‌شناسی | درمان و مشاوره | آموزش و پرورش | ریاضیات | قانون و دولت</t>
+          <t>پزشکی و دندان‌پزشکی | روان‌شناسی | خدمات مشتری و شخصی | زبان انگلیسی | زیست‌شناسی | جامعه‌شناسی و انسان‌شناسی | درمان و مشاوره | آموزش و پرورش | ریاضیات | قانون و دولت</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک نوشتاری | درک شنیداری | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | بیان نوشتاری | استدلال استقرایی | دید نزدیک | تشخیص گفتار | وضوح گفتار | نظم‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | ثبات دست و بازو | اشتراک زمانی | سرعت ادراکی | انعطاف‌پذیری بستار | حافظه | مهارت انگشتان | مهارت دستی | تجسم | سرعت بستار | اصالت</t>
+          <t>درک کتبی | درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | بیان کتبی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | ثبات دست و بازو | تقسیم توجه | سرعت ادراکی | انعطاف‌پذیری بستار | حفظ کردن | مهارت انگشتان | مهارت دستی | تجسم | سرعت بستار | اصالت</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>بحث‌های رودررو با افراد و درون تیم‌ها | نزدیکی فیزیکی | تماس با دیگران | ایمیل | مکالمات تلفنی | تکرار تصمیم‌گیری | محیط داخلی، دارای کنترل محیطی | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | پیامد خطا | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | در معرض بیماری یا عفونت | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا صحیح بودن | برخورد با مشتریان خارجی یا عموم مردم | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارکنان | فشار زمانی | موقعیت‌های تعارض | نامه‌ها و یادداشت‌های کتبی | صرف زمان برای استفاده از دست‌ها جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | در معرض آلاینده‌ها</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | ارتباط با دیگران | ایمیل | مکالمات تلفنی | فراوانی تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | پیامد خطا | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارکنان | فشار زمانی | موقعیت‌های تعارض | نامه‌ها و یادداشت‌های کتبی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | قرار گرفتن در معرض آلاینده‌ها</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | پرستاران روانپزشکی پیشرفته | متخصصان بیهوشی | پرستاران بالینی متخصص | پرستاران مراقبت‌های ویژه | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | پزشکان بیمارستانی | پرستاران عملی و حرفه‌ای دارای مجوز | ماماها | متخصصان مغز و اعصاب | پرستاران بیهوشی | پرستاران متخصص | متخصصان زنان و زایمان | پیراپزشکان | متخصصان کودکان، عمومی | دستیاران پزشک | روانپزشکان | پرستاران ثبت‌نام شده</t>
+          <t>پرستاران مراقبت‌های ویژه | پرستاران پیشرفته روانپزشکی | متخصصان بیهوشی | متخصصان پرستاری بالینی | پرستاران بخش مراقبت‌های ویژه | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | پزشکان بیمارستانی | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | ماماها | متخصصان مغز و اعصاب | پرستاران بیهوشی | پرستاران متخصص | متخصصان زنان و زایمان | پارامدیک‌ها | متخصصان کودکان، عمومی | دستیاران پزشک | روان‌پزشکان | پرستاران ثبت‌شده</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -612,37 +612,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ACNP (Acute Care Nurse Practitioner) | ARNP Specialist (Advanced Registered Nurse Practitioner Specialist) | Adult Nurse Practitioner | Advanced Practice Registered Nurse (APRN) | Family Nurse Practitioner (FNP) | Family Practice Certified Advanced Registered Nurse Practitioner | Gastroenterology Nurse Practitioner | Nurse Practitioner (NP) | Pediatric Nurse Practitioner (PNP) | Women's Health Care Nurse Practitioner</t>
+          <t>ACNP (پرستار متخصص مراقبت حاد) | ARNP (پرستار متخصص پیشرفته دارای پروانه) | پرستار متخصص بزرگسالان | پرستار پیشرفته دارای پروانه (APRN) | پرستار متخصص خانواده (FNP) | پرستار پیشرفته دارای پروانه و گواهی طب خانواده | پرستار متخصص گوارش | پرستار متخصص (NP) | پرستار متخصص کودکان (PNP) | پرستار متخصص سلامت زنان</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Allscripts Professional EHR | Amkai AmkaiCharts | Bizmatics PrognoCIS EMR | Cerner Millennium | Epic Systems | GE Healthcare Centricity EMR | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | نرم‌افزار MEDITECH | نرم‌افزار کدگذاری وضعیت پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | Medscribbler Enterprise | MicroFour PracticeStudio.NET EMR | Microsoft Access | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Word | NextGen Healthcare Information Systems EMR | PCC Pediatric Partner | نرم‌افزار مدیریت بیمار | SOAPware EMR | StatCom Patient Flow Logistics Enterprise Suite | SynaMed EMR | Texas Medical Software SpringCharts EMR | نرم‌افزار مرورگر وب | نرم‌افزار e-MDs | نرم‌افزار eClinicalWorks EHR</t>
+          <t>Allscripts Professional EHR | Amkai AmkaiCharts | Bizmatics PrognoCIS EMR | Cerner Millennium | Epic Systems | GE Healthcare Centricity EMR | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | نرم‌افزار MEDITECH | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | Medscribbler Enterprise | MicroFour PracticeStudio.NET EMR | Microsoft Access | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Word | NextGen Healthcare Information Systems EMR | PCC Pediatric Partner | نرم‌افزار مدیریت بیمار | SOAPware EMR | StatCom Patient Flow Logistics Enterprise Suite | SynaMed EMR | Texas Medical Software SpringCharts EMR | نرم‌افزار مرورگر وب | نرم‌افزار e-MDs | نرم‌افزار eClinicalWorks EHR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخنوری | نوشتن | پایش | یادگیری فعال | علوم | راهبردهای یادگیری | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | علوم | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زبان انگلیسی | زیست‌شناسی | روان‌شناسی | خدمات مشتری و شخصی | درمان و مشاوره | آموزش و پرورش | جامعه‌شناسی و مردم‌شناسی | ریاضیات | شیمی | مدیریت و اداره | رایانه و الکترونیک | ایمنی و امنیت عمومی | ارتباطات و رسانه | قانون و دولت</t>
+          <t>پزشکی و دندان‌پزشکی | زبان انگلیسی | زیست‌شناسی | روان‌شناسی | خدمات مشتری و شخصی | درمان و مشاوره | آموزش و پرورش | جامعه‌شناسی و انسان‌شناسی | ریاضیات | شیمی | مدیریت و اداره | رایانه و الکترونیک | ایمنی و امنیت عمومی | ارتباطات و رسانه | قانون و دولت</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک نوشتاری | استدلال استقرایی | حساسیت به مسئله | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | دید نزدیک | درک شنیداری | نظم‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | انعطاف‌پذیری بستار | سرعت بستار | تشخیص رنگ بصری | دید دور | اشتراک زمانی | توجه انتخابی | سرعت ادراکی | حافظه | توانایی عددی | اصالت</t>
+          <t>درک کتبی | استدلال استقرایی | حساسیت به مسئله | بیان شفاهی | بیان کتبی | استدلال قیاسی | بینایی نزدیک | درک شفاهی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | انعطاف‌پذیری بستار | سرعت بستار | تشخیص رنگ بصری | بینایی دور | تقسیم توجه | توجه انتخابی | سرعت ادراکی | حفظ کردن | توانایی عددی | اصالت</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>بحث‌های رودررو با افراد و درون تیم‌ها | مکالمات تلفنی | ایمیل | در معرض بیماری یا عفونت | کار با یا مشارکت در یک گروه کاری یا تیم | تماس با دیگران | آزادی در تصمیم‌گیری | تکرار تصمیم‌گیری | اهمیت دقیق یا صحیح بودن | محیط داخلی، دارای کنترل محیطی | پیامد خطا | نزدیکی فیزیکی | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | برخورد با مشتریان خارجی یا عموم مردم | فشار زمانی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | سلامت و ایمنی سایر کارکنان | نامه‌ها و یادداشت‌های کتبی | نتایج کاری و خروجی‌های سایر کارکنان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ایمیل | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | پیامد خطا | نزدیکی فیزیکی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | تعامل با مشتریان خارجی یا عموم مردم | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سلامت و ایمنی سایر کارکنان | نامه‌ها و یادداشت‌های کتبی | پیامدهای کاری و نتایج سایر کارکنان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | پرستاران روانپزشکی پیشرفته | متخصصان بیهوشی | پرستاران بالینی متخصص | پرستاران مراقبت‌های ویژه | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | پرستاران عملی و حرفه‌ای دارای مجوز | متخصصان مغز و اعصاب | پرستاران بیهوشی | ماماها | متخصصان زنان و زایمان | پیراپزشکان | جراحان کودکان | متخصصان کودکان، عمومی | دستیاران پزشک | روانپزشکان | پرستاران ثبت‌نام شده</t>
+          <t>پرستاران مراقبت‌های ویژه | پرستاران پیشرفته روانپزشکی | متخصصان بیهوشی | متخصصان قلب | متخصصان پرستاری بالینی | پرستاران بخش مراقبت‌های ویژه | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | متخصصان مغز و اعصاب | پرستاران بیهوشی | ماماها | متخصصان زنان و زایمان | پارامدیک‌ها | جراحان کودکان | متخصصان کودکان، عمومی | دستیاران پزشک | روان‌پزشکان | پرستاران ثبت‌شده</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Audiologist | Audiology Doctor (AUD) | Certificate of Clinical Competence in Audiology Licensed Audiologist (CCC-A Licensed Audiologist) | Clinical Audiologist | Dispensing Audiologist | Educational Audiologist | Forensic Audiologist | Industrial Audiologist | Pediatric Audiologist | Staff Audiologist</t>
+          <t>شنوایی‌شناس | دکترای شنوایی‌شناسی (AUD) | شنوایی‌شناس دارای پروانه و گواهی صلاحیت بالینی (CCC-A) | شنوایی‌شناس بالینی | شنوایی‌شناس تجویزکننده سمعک | شنوایی‌شناس آموزشی | شنوایی‌شناس قضایی | شنوایی‌شناس صنعتی | شنوایی‌شناس کودکان | شنوایی‌شناس کادر درمان</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخنوری | نوشتن | یادگیری فعال | پایش | راهبردهای یادگیری | علوم</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتری و شخصی | درمان و مشاوره | روان‌شناسی | پزشکی و دندانپزشکی | زبان انگلیسی | فروش و بازاریابی | رایانه و الکترونیک | زیست‌شناسی | آموزش و پرورش | اداری | مدیریت و اداره | اقتصاد و حسابداری | پرسنل و منابع انسانی | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | درمان و مشاوره | روان‌شناسی | پزشکی و دندان‌پزشکی | زبان انگلیسی | فروش و بازاریابی | رایانه و الکترونیک | زیست‌شناسی | آموزش و پرورش | اداری | مدیریت و اداره | اقتصاد و حسابداری | پرسنل و منابع انسانی | ریاضیات</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | دید نزدیک | تشخیص گفتار | نظم‌دهی اطلاعات | حساسیت شنوایی | توجه شنیداری | انعطاف‌پذیری دسته‌بندی | سرعت ادراکی | انعطاف‌پذیری بستار | اصالت | دقت کنترل | سرعت بستار | روانی ایده‌ها | مهارت انگشتان | ثبات دست و بازو</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | ترتیب‌دهی اطلاعات | حساسیت شنوایی | توجه شنیداری | انعطاف‌پذیری دسته‌بندی | سرعت ادراکی | انعطاف‌پذیری بستار | اصالت | دقت کنترل | سرعت بستار | روانی ایده‌ها | مهارت انگشتان | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>بحث‌های رودررو با افراد و درون تیم‌ها | ایمیل | مکالمات تلفنی | تماس با دیگران | برخورد با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا صحیح بودن | محیط داخلی، دارای کنترل محیطی | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | تکرار تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | در معرض بیماری یا عفونت | صرف زمان برای نشستن | صرف زمان برای استفاده از دست‌ها جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | مکالمات تلفنی | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | فراوانی تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | صرف زمان برای نشستن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>متخصصان آلرژی و ایمنی‌شناسی | متخصصان قلب | کایروپراکتورها | متخصصان پوست | پزشکان طب اورژانس | پزشکان داخلی عمومی | متخصصان سمعک | متخصصان مغز و اعصاب | پرستاران متخصص | کاردرمانگران | دستیاران کاردرمانی | متخصصان چشم، به جز کودکان | اپتومتریست‌ها | جراحان ارتوپد، به جز کودکان | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | پزشکان، آسیب‌شناسان | روانپزشکان | آسیب‌شناسان گفتار-زبان</t>
+          <t>متخصصان آلرژی و ایمونولوژی | متخصصان قلب | کایروپراکتورها | متخصصان پوست | پزشکان طب اورژانس | پزشکان داخلی عمومی | متخصصان سمعک | متخصصان مغز و اعصاب | پرستاران متخصص | کاردرمانگران | کمک‌یاران کاردرمانی | چشم‌پزشکان، به‌جز کودکان | اپتومتریست‌ها | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | پزشکان، آسیب‌شناسان | روان‌پزشکان | آسیب‌شناسان گفتار و زبان</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -726,37 +726,37 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Medical Doctor (MD) | Obstetrical Anesthesiologist | Staff Anesthesiologist | Staff Anesthetist</t>
+          <t>دکترای پزشکی (MD) | متخصص بیهوشی زایمان | متخصص بیهوشی کادر درمان | کارشناس بیهوشی کادر درمان</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AetherPalm InfusiCalc | نرم‌افزار دستگاه بیهوشی | AtStaff Physician Scheduler | نرم‌افزار پایگاه داده دارو | EDImis Anesthesia Manager | نرم‌افزار سوابق پزشکی الکترونیک EMR | Epic Systems | Healthpac Medical Billing | نرم‌افزار MEDITECH | نرم‌افزار ماشین‌حساب پزشکی | Microsoft Access | Microsoft Excel | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Skyscape 5-Minute Clinical Consult | Skyscape AnesthesiaDrugs | نرم‌افزار مرورگر وب</t>
+          <t>AetherPalm InfusiCalc | نرم‌افزار دستگاه بیهوشی | AtStaff Physician Scheduler | نرم‌افزار پایگاه داده دارو | EDImis Anesthesia Manager | نرم‌افزار پرونده الکترونیک سلامت EMR | Epic Systems | Healthpac Medical Billing | نرم‌افزار MEDITECH | نرم‌افزار ماشین‌حساب پزشکی | Microsoft Access | Microsoft Excel | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Skyscape 5-Minute Clinical Consult | Skyscape AnesthesiaDrugs | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | گوش دادن فعال | پایش | علوم | نوشتن | درک مطلب | سخنوری | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
+          <t>تفکر انتقادی | گوش دادن فعال | نظارت | علوم | نگارش | درک مطلب | سخن گفتن | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | زبان انگلیسی | شیمی | خدمات مشتری و شخصی | روان‌شناسی | فیزیک | ریاضیات | آموزش و پرورش | مدیریت و اداره</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | زبان انگلیسی | شیمی | خدمات مشتری و شخصی | روان‌شناسی | فیزیک | ریاضیات | آموزش و پرورش | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | استدلال قیاسی | درک شنیداری | استدلال استقرایی | درک نوشتاری | دید نزدیک | بیان شفاهی | بیان نوشتاری | نظم‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری بستار | سرعت ادراکی | ثبات دست و بازو | تشخیص گفتار | وضوح گفتار | مهارت انگشتان | روانی ایده‌ها | دقت کنترل | مهارت دستی | اشتراک زمانی | دید دور | جهت‌گیری پاسخ | توانایی عددی | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی</t>
+          <t>حساسیت به مسئله | استدلال قیاسی | درک شفاهی | استدلال استقرایی | درک کتبی | بینایی نزدیک | بیان شفاهی | بیان کتبی | ترتیب‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری بستار | سرعت ادراکی | ثبات دست و بازو | تشخیص گفتار | وضوح گفتار | مهارت انگشتان | روانی ایده‌ها | دقت کنترل | مهارت دستی | تقسیم توجه | بینایی دور | جهت‌گیری پاسخ | توانایی عددی | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>بحث‌های رودررو با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | اهمیت دقیق یا صحیح بودن | تماس با دیگران | نزدیکی فیزیکی | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تکرار تصمیم‌گیری | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | در معرض بیماری یا عفونت | پیامد خطا | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | در معرض آلاینده‌ها | سلامت و ایمنی سایر کارکنان | پوشیدن تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، مهار ایمنی، لباس‌های محافظ کامل یا محافظ تابش | فشار زمانی | در معرض تابش | نتایج کاری و خروجی‌های سایر کارکنان | صرف زمان برای استفاده از دست‌ها جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سطح رقابت | اهمیت تکرار وظایف مشابه | برخورد با مشتریان خارجی یا عموم مردم</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | ارتباط با دیگران | نزدیکی فیزیکی | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | پیامد خطا | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض آلاینده‌ها | سلامت و ایمنی سایر کارکنان | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | فشار زمانی | قرار گرفتن در معرض تابش | پیامدهای کاری و نتایج سایر کارکنان | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سطح رقابت | اهمیت تکرار وظایف یکسان | تعامل با مشتریان خارجی یا عموم مردم</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | دستیاران متخصص بیهوشی | متخصصان قلب | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | متخصصان مغز و اعصاب | پرستاران بیهوشی | پرستاران متخصص | متخصصان زنان و زایمان | متخصصان چشم، به جز کودکان | جراحان ارتوپد، به جز کودکان | پیراپزشکان | جراحان کودکان | پزشکان طب فیزیکی و توانبخشی | دستیاران پزشک | پرستاران ثبت‌نام شده | درمانگران تنفسی | دستیاران جراحی | متخصصان اورولوژی</t>
+          <t>پرستاران مراقبت‌های ویژه | دستیاران متخصص بیهوشی | متخصصان قلب | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | متخصصان مغز و اعصاب | پرستاران بیهوشی | پرستاران متخصص | متخصصان زنان و زایمان | چشم‌پزشکان، به‌جز کودکان | جراحان ارتوپد، به‌جز کودکان | پارامدیک‌ها | جراحان کودکان | پزشکان طب فیزیکی و توانبخشی | دستیاران پزشک | پرستاران ثبت‌شده | درمانگران تنفسی | دستیاران جراحی | اورولوژیست‌ها</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cardiac Electrophysiologist | Cardiologist | Cardiovascular Disease Specialist | Cardiovascular Physician | Echocardiographer | Heart Specialist | Interventional Cardiologist | Noninvasive Cardiologist | Pediatric Cardiologist | Preventive Cardiologist</t>
+          <t>متخصص الکتروفیزیولوژی قلب | متخصص قلب | متخصص بیماری‌های قلب و عروق | پزشک قلب و عروق | متخصص اکوکاردیوگرافی | متخصص قلب | متخصص قلب مداخله‌ای | متخصص قلب غیرتهاجمی | متخصص قلب کودکان | متخصص قلب پیشگیری</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخنوری | علوم | پایش | یادگیری فعال | نوشتن</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | شیمی | خدمات مشتری و شخصی | زبان انگلیسی | روان‌شناسی | آموزش و پرورش | فیزیک | مدیریت و اداره | درمان و مشاوره</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | شیمی | خدمات مشتری و شخصی | زبان انگلیسی | روان‌شناسی | آموزش و پرورش | فیزیک | مدیریت و اداره | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | نظم‌دهی اطلاعات | دید نزدیک | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | ثبات دست و بازو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | اشتراک زمانی | دقت کنترل | درک عمق</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | ثبات دست و بازو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | تقسیم توجه | دقت کنترل | درک عمق</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>در معرض بیماری یا عفونت | نزدیکی فیزیکی | تماس با دیگران | برخورد با مشتریان خارجی یا عموم مردم | پیامد خطا | اهمیت دقیق یا صحیح بودن | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | تکرار تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | بحث‌های رودررو با افراد و درون تیم‌ها | مکالمات تلفنی | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | محیط داخلی، دارای کنترل محیطی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | در معرض تابش | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | نزدیکی فیزیکی | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | پیامد خطا | اهمیت دقیق یا درست بودن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض تابش | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | متخصصان آلرژی و ایمنی‌شناسی | دستیاران متخصص بیهوشی | متخصصان بیهوشی | تکنسین‌ها و کارشناسان قلبی-عروقی | متخصصان پوست | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | متخصصان مغز و اعصاب | پرستاران متخصص | متخصصان زنان و زایمان | متخصصان چشم، به جز کودکان | جراحان ارتوپد، به جز کودکان | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | دستیاران پزشک | رادیولوژیست‌ها | متخصصان اورولوژی</t>
+          <t>پرستاران مراقبت‌های ویژه | متخصصان آلرژی و ایمونولوژی | دستیاران متخصص بیهوشی | متخصصان بیهوشی | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | متخصصان پوست | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | متخصصان مغز و اعصاب | پرستاران متخصص | متخصصان زنان و زایمان | چشم‌پزشکان، به‌جز کودکان | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | دستیاران پزشک | رادیولوژیست‌ها | اورولوژیست‌ها</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Board Certified Dermatologist | Dermatologist MD (Dermatologist Medical Doctor) | Dermatologist Physician | Dermatopathologist | Doctor | MD (Medical Doctor) | Mohs Micrographic Surgeon | Mohs Surgeon | Pediatric Dermatologist | Practicing Dermatologist</t>
+          <t>متخصص پوست دارای بورد تخصصی | پزشک متخصص پوست (Dermatologist MD) | پزشک متخصص پوست | متخصص آسیب‌شناسی پوست | پزشک | MD (دکترای پزشکی) | جراح میکروگرافیک موس | جراح موس | متخصص پوست کودکان | متخصص شاغل پوست</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | سخنوری | یادگیری فعال | علوم | نوشتن | پایش | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن | یادگیری فعال | علوم | نگارش | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | خدمات مشتری و شخصی | زبان انگلیسی | مدیریت و اداره | آموزش و پرورش | زیست‌شناسی | پرسنل و منابع انسانی | روان‌شناسی | رایانه و الکترونیک</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | زبان انگلیسی | مدیریت و اداره | آموزش و پرورش | زیست‌شناسی | پرسنل و منابع انسانی | روان‌شناسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | بیان شفاهی | درک شنیداری | استدلال قیاسی | استدلال استقرایی | درک نوشتاری | دید نزدیک | بیان نوشتاری | نظم‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | تشخیص رنگ بصری | توجه انتخابی | دید دور | مهارت انگشتان | ثبات دست و بازو | سرعت ادراکی | حافظه | اصالت | روانی ایده‌ها</t>
+          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | درک کتبی | بینایی نزدیک | بیان کتبی | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | تشخیص رنگ بصری | توجه انتخابی | بینایی دور | مهارت انگشتان | ثبات دست و بازو | سرعت ادراکی | حفظ کردن | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>آزادی در تصمیم‌گیری | بحث‌های رودررو با افراد و درون تیم‌ها | تماس با دیگران | برخورد با مشتریان خارجی یا عموم مردم | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا صحیح بودن | ایمیل | سلامت و ایمنی سایر کارکنان | در معرض بیماری یا عفونت | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | تکرار تصمیم‌گیری | نزدیکی فیزیکی | نامه‌ها و یادداشت‌های کتبی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | محیط داخلی، دارای کنترل محیطی | نتایج کاری و خروجی‌های سایر کارکنان | پیامد خطا | صرف زمان برای ایستادن | فشار زمانی | سطح رقابت</t>
+          <t>آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | ایمیل | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | نزدیکی فیزیکی | نامه‌ها و یادداشت‌های کتبی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | محیط داخلی، دارای کنترل شرایط محیطی | پیامدهای کاری و نتایج سایر کارکنان | پیامد خطا | صرف زمان برای ایستادن | فشار زمانی | سطح رقابت</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>متخصصان آلرژی و ایمنی‌شناسی | متخصصان بیهوشی | متخصصان قلب | کایروپراکتورها | پزشکان طب اورژانس | پزشکان داخلی عمومی | پزشکان ناتوروپاتیک | متخصصان مغز و اعصاب | پرستاران متخصص | متخصصان زنان و زایمان | متخصصان چشم، به جز کودکان | اپتومتریست‌ها | جراحان دهان و فک و صورت | جراحان ارتوپد، به جز کودکان | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | دستیاران پزشک | متخصصان پا | متخصصان اورولوژی</t>
+          <t>متخصصان آلرژی و ایمونولوژی | متخصصان بیهوشی | متخصصان قلب | کایروپراکتورها | پزشکان طب اورژانس | پزشکان داخلی عمومی | پزشکان ناتوروپاتی | متخصصان مغز و اعصاب | پرستاران متخصص | متخصصان زنان و زایمان | چشم‌پزشکان، به‌جز کودکان | اپتومتریست‌ها | جراحان دهان و فک و صورت | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | دستیاران پزشک | پزشکان پا | اورولوژیست‌ها</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Attending Emergency Physician | Attending Physician | Emergency MD (Emergency Medicine Doctor) | Emergency Medicine Physician (EM Physician) | Emergency Physician | MD (Medical Doctor) | Physician</t>
+          <t>پزشک ارشد اورژانس | پزشک معالج ارشد | پزشک طب اورژانس (Emergency MD) | پزشک طب اورژانس (EM Physician) | پزشک اورژانس | MD (دکترای پزشکی) | پزشک</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | سخنوری | پایش | نوشتن | یادگیری فعال | راهبردهای یادگیری | علوم</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زبان انگلیسی | زیست‌شناسی | روان‌شناسی | درمان و مشاوره | خدمات مشتری و شخصی | آموزش و پرورش | ایمنی و امنیت عمومی | شیمی | ریاضیات</t>
+          <t>پزشکی و دندان‌پزشکی | زبان انگلیسی | زیست‌شناسی | روان‌شناسی | درمان و مشاوره | خدمات مشتری و شخصی | آموزش و پرورش | ایمنی و امنیت عمومی | شیمی | ریاضیات</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شنیداری | درک نوشتاری | بیان نوشتاری | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | نظم‌دهی اطلاعات | دید نزدیک | انعطاف‌پذیری بستار | روانی ایده‌ها | توجه انتخابی | اصالت | انعطاف‌پذیری دسته‌بندی | سرعت بستار | ثبات دست و بازو | سرعت ادراکی | حافظه | مهارت انگشتان | دید دور | مهارت دستی | اشتراک زمانی | تشخیص رنگ بصری | سرعت مچ-انگشت | هماهنگی چند اندام</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | ترتیب‌دهی اطلاعات | بینایی نزدیک | انعطاف‌پذیری بستار | روانی ایده‌ها | توجه انتخابی | اصالت | انعطاف‌پذیری دسته‌بندی | سرعت بستار | ثبات دست و بازو | سرعت ادراکی | حفظ کردن | مهارت انگشتان | بینایی دور | مهارت دستی | تقسیم توجه | تشخیص رنگ بصری | سرعت مچ و انگشتان | هماهنگی چند عضو</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>در معرض بیماری یا عفونت | محیط داخلی، دارای کنترل محیطی | تماس با دیگران | مکالمات تلفنی | آزادی در تصمیم‌گیری | پیامد خطا | بحث‌های رودررو با افراد و درون تیم‌ها | اهمیت دقیق یا صحیح بودن | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | برخورد با مشتریان خارجی یا عموم مردم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | ایمیل | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | تکرار تصمیم‌گیری | موقعیت‌های تعارض | در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | سطح رقابت | سلامت و ایمنی سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | برخورد با افراد خشن یا دارای پرخاشگری فیزیکی | نتایج کاری و خروجی‌های سایر کارکنان | اهمیت تکرار وظایف مشابه</t>
+          <t>قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | مکالمات تلفنی | آزادی در تصمیم‌گیری | پیامد خطا | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | تعامل با مشتریان خارجی یا عموم مردم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | ایمیل | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فراوانی تصمیم‌گیری | موقعیت‌های تعارض | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سطح رقابت | سلامت و ایمنی سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | برخورد با افراد خشن یا از نظر فیزیکی پرخاشگر | پیامدهای کاری و نتایج سایر کارکنان | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | متخصصان بیهوشی | متخصصان قلب | پرستاران بالینی متخصص | پرستاران مراقبت‌های ویژه | تکنسین‌های فوریت‌های پزشکی | پزشکان خانواده | پزشکان داخلی عمومی | پزشکان بیمارستانی | متخصصان مغز و اعصاب | پرستاران متخصص | متخصصان زنان و زایمان | جراحان ارتوپد، به جز کودکان | پیراپزشکان | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | دستیاران پزشک | روانپزشکان | پرستاران ثبت‌نام شده</t>
+          <t>پرستاران مراقبت‌های ویژه | متخصصان بیهوشی | متخصصان قلب | متخصصان پرستاری بالینی | پرستاران بخش مراقبت‌های ویژه | تکنسین‌های فوریت‌های پزشکی | پزشکان خانواده | پزشکان داخلی عمومی | پزشکان بیمارستانی | متخصصان مغز و اعصاب | پرستاران متخصص | متخصصان زنان و زایمان | جراحان ارتوپد، به‌جز کودکان | پارامدیک‌ها | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | دستیاران پزشک | روان‌پزشکان | پرستاران ثبت‌شده</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -954,37 +954,37 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Board Certified Family Physician | Family Medicine Physician | Family Physician | Family Practice Medical Doctor (FP MD) | Family Practice Physician (FP Physician) | Family Practitioner | Medical Doctor (MD) | Medical Staff Physician | Physician | Primary Care Physician</t>
+          <t>پزشک خانواده دارای بورد تخصصی | پزشک طب خانواده | پزشک خانواده | پزشک طب خانواده (FP MD) | پزشک طب خانواده (FP Physician) | پزشک عمومی خانواده | دکترای پزشکی (MD) | پزشک کادر درمان | پزشک | پزشک مراقبت اولیه</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Acrendo Medical Software Family Practice EMR | Allscripts Professional EHR | نرم‌افزار صورت‌حساب | Brickell Research Brickell Medical Office | ChartWare EMR | نرم‌افزار ایمیل | Epic Systems | Epocrates | Greenway Health PrimeSuite | نرم‌افزار MEDITECH | Med Math | MedcomSoft Record | نرم‌افزار مرجع پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Excel | نرم‌افزار Microsoft Office | Misys Healthcare Systems Mysis Tiger | Practice Partner Total Practice Partner | نرم‌افزار مدیریت مطب PMS | SOAPware EMR | نرم‌افزار زمان‌بندی | نرم‌افزار مرورگر وب | نرم‌افزار e-MDs | نرم‌افزار e-MDs topsE&amp;M Coder | نرم‌افزار eClinicalWorks EHR</t>
+          <t>Acrendo Medical Software Family Practice EMR | Allscripts Professional EHR | نرم‌افزار صدور صورتحساب | Brickell Research Brickell Medical Office | ChartWare EMR | نرم‌افزار ایمیل | Epic Systems | Epocrates | Greenway Health PrimeSuite | نرم‌افزار MEDITECH | Med Math | MedcomSoft Record | نرم‌افزار کدگذاری رویه‌های پزشکی | نرم‌افزار مرجع پزشکی | Microsoft Excel | نرم‌افزار Microsoft Office | Misys Healthcare Systems Mysis Tiger | Practice Partner Total Practice Partner | نرم‌افزار مدیریت مطب PMS | SOAPware EMR | نرم‌افزار زمان‌بندی | نرم‌افزار مرورگر وب | نرم‌افزار e-MDs | نرم‌افزار e-MDs topsE&amp;M Coder | نرم‌افزار eClinicalWorks EHR</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | سخنوری | نوشتن | پایش | یادگیری فعال | علوم | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن | نگارش | نظارت | یادگیری فعال | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زبان انگلیسی | درمان و مشاوره | روان‌شناسی | زیست‌شناسی | خدمات مشتری و شخصی | رایانه و الکترونیک | ریاضیات | آموزش و پرورش | جامعه‌شناسی و مردم‌شناسی | قانون و دولت</t>
+          <t>پزشکی و دندان‌پزشکی | زبان انگلیسی | درمان و مشاوره | روان‌شناسی | زیست‌شناسی | خدمات مشتری و شخصی | رایانه و الکترونیک | ریاضیات | آموزش و پرورش | جامعه‌شناسی و انسان‌شناسی | قانون و دولت</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شنیداری | بیان شفاهی | استدلال قیاسی | درک نوشتاری | استدلال استقرایی | بیان نوشتاری | وضوح گفتار | دید نزدیک | تشخیص گفتار | انعطاف‌پذیری بستار | توجه انتخابی | نظم‌دهی اطلاعات | روانی ایده‌ها | اشتراک زمانی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | اصالت</t>
+          <t>حساسیت به مسئله | درک شفاهی | بیان شفاهی | استدلال قیاسی | درک کتبی | استدلال استقرایی | بیان کتبی | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | انعطاف‌پذیری بستار | توجه انتخابی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | تقسیم توجه | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | اصالت</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>تماس با دیگران | بحث‌های رودررو با افراد و درون تیم‌ها | تکرار تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | پیامد خطا | نزدیکی فیزیکی | محیط داخلی، دارای کنترل محیطی | در معرض بیماری یا عفونت | اهمیت دقیق یا صحیح بودن | فشار زمانی | مکالمات تلفنی | برخورد با مشتریان خارجی یا عموم مردم | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | نتایج کاری و خروجی‌های سایر کارکنان | نامه‌ها و یادداشت‌های کتبی | ایمیل | صرف زمان برای استفاده از دست‌ها جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سلامت و ایمنی سایر کارکنان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | موقعیت‌های تعارض</t>
+          <t>ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | پیامد خطا | نزدیکی فیزیکی | محیط داخلی، دارای کنترل شرایط محیطی | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | اهمیت دقیق یا درست بودن | فشار زمانی | مکالمات تلفنی | تعامل با مشتریان خارجی یا عموم مردم | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | نامه‌ها و یادداشت‌های کتبی | ایمیل | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سلامت و ایمنی سایر کارکنان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | موقعیت‌های تعارض</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>پرستاران روانپزشکی پیشرفته | متخصصان بیهوشی | متخصصان قلب | پرستاران بالینی متخصص | پزشکان طب اورژانس | پزشکان داخلی عمومی | پزشکان بیمارستانی | پزشکان ناتوروپاتیک | متخصصان مغز و اعصاب | ماماها | پرستاران متخصص | متخصصان زنان و زایمان | جراحان ارتوپد، به جز کودکان | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | دستیاران پزشک | پزشکان طب پیشگیری | روانپزشکان | پرستاران ثبت‌نام شده</t>
+          <t>پرستاران پیشرفته روانپزشکی | متخصصان بیهوشی | متخصصان قلب | متخصصان پرستاری بالینی | پزشکان طب اورژانس | پزشکان داخلی عمومی | پزشکان بیمارستانی | پزشکان ناتوروپاتی | متخصصان مغز و اعصاب | ماماها | پرستاران متخصص | متخصصان زنان و زایمان | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | دستیاران پزشک | پزشکان طب پیشگیری | روان‌پزشکان | پرستاران ثبت‌شده</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1011,37 +1011,37 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Doctor | Gastroenterologist | General Internal Medicine Physician | General Internist | Internal Medicine Doctor | Internal Medicine Physician (IM Physician) | Internist | Medical Doctor (MD) | Physician | Primary Care Physician</t>
+          <t>پزشک | متخصص گوارش | پزشک طب داخلی عمومی | متخصص داخلی عمومی | پزشک طب داخلی | پزشک طب داخلی (IM Physician) | متخصص داخلی | دکترای پزشکی (MD) | پزشک | پزشک مراقبت اولیه</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Allscripts Professional EHR | نرم‌افزار صورت‌حساب | Brickell Research Brickell Medical Office | ChartWare EMR | نرم‌افزار ایمیل | Epic Systems | Epocrates | GE Healthcare Centricity EMR | Greenway Health PrimeSuite | نرم‌افزار MEDITECH | Med Math | MedcomSoft Record | نرم‌افزار مرجع پزشکی | MicroFocus GroupWise | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Misys Healthcare Systems Mysis Tiger | Practice Partner Total Practice Partner | نرم‌افزار مدیریت مطب PMS | SOAPware EMR | نرم‌افزار زمان‌بندی | نرم‌افزار مرورگر وب | نرم‌افزار e-MDs | نرم‌افزار e-MDs topsE&amp;M Coder | نرم‌افزار eClinicalWorks EHR</t>
+          <t>Allscripts Professional EHR | نرم‌افزار صدور صورتحساب | Brickell Research Brickell Medical Office | ChartWare EMR | نرم‌افزار ایمیل | Epic Systems | Epocrates | GE Healthcare Centricity EMR | Greenway Health PrimeSuite | نرم‌افزار MEDITECH | Med Math | MedcomSoft Record | نرم‌افزار مرجع پزشکی | MicroFocus GroupWise | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Misys Healthcare Systems Mysis Tiger | Practice Partner Total Practice Partner | نرم‌افزار مدیریت مطب PMS | SOAPware EMR | نرم‌افزار زمان‌بندی | نرم‌افزار مرورگر وب | نرم‌افزار e-MDs | نرم‌افزار e-MDs topsE&amp;M Coder | نرم‌افزار eClinicalWorks EHR</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | درک مطلب | نوشتن | تفکر انتقادی | علوم | سخنوری | یادگیری فعال | پایش | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | علوم | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | درمان و مشاوره | روان‌شناسی | آموزش و پرورش | زبان انگلیسی | مدیریت و اداره | رایانه و الکترونیک | خدمات مشتری و شخصی | ریاضیات | شیمی | پرسنل و منابع انسانی | ایمنی و امنیت عمومی | اداری | اقتصاد و حسابداری</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | درمان و مشاوره | روان‌شناسی | آموزش و پرورش | زبان انگلیسی | مدیریت و اداره | رایانه و الکترونیک | خدمات مشتری و شخصی | ریاضیات | شیمی | پرسنل و منابع انسانی | ایمنی و امنیت عمومی | اداری | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شنیداری | استدلال استقرایی | بیان شفاهی | درک نوشتاری | استدلال قیاسی | بیان نوشتاری | نظم‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | دید نزدیک | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری بستار | سرعت ادراکی | توجه انتخابی | روانی ایده‌ها | دید دور | حافظه | توانایی عددی | استدلال ریاضی | اصالت</t>
+          <t>حساسیت به مسئله | درک شفاهی | استدلال استقرایی | بیان شفاهی | درک کتبی | استدلال قیاسی | بیان کتبی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری بستار | سرعت ادراکی | توجه انتخابی | روانی ایده‌ها | بینایی دور | حفظ کردن | توانایی عددی | استدلال ریاضی | اصالت</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>در معرض بیماری یا عفونت | محیط داخلی، دارای کنترل محیطی | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | ایمیل | مکالمات تلفنی | تماس با دیگران | بحث‌های رودررو با افراد و درون تیم‌ها | اهمیت دقیق یا صحیح بودن | تعیین وظایف، اولویت‌ها و اهداف | تکرار تصمیم‌گیری | پیامد خطا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | برخورد با مشتریان خارجی یا عموم مردم | سلامت و ایمنی سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | اهمیت تکرار وظایف مشابه | نامه‌ها و یادداشت‌های کتبی | نتایج کاری و خروجی‌های سایر کارکنان | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات</t>
+          <t>قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | ایمیل | مکالمات تلفنی | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | فراوانی تصمیم‌گیری | پیامد خطا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | تعامل با مشتریان خارجی یا عموم مردم | سلامت و ایمنی سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت تکرار وظایف یکسان | نامه‌ها و یادداشت‌های کتبی | پیامدهای کاری و نتایج سایر کارکنان | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>متخصصان آلرژی و ایمنی‌شناسی | متخصصان بیهوشی | متخصصان قلب | پرستاران بالینی متخصص | متخصصان پوست | پزشکان طب اورژانس | پزشکان خانواده | پزشکان بیمارستانی | پزشکان ناتوروپاتیک | متخصصان مغز و اعصاب | پرستاران متخصص | متخصصان زنان و زایمان | متخصصان چشم، به جز کودکان | جراحان ارتوپد، به جز کودکان | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | دستیاران پزشک | روانپزشکان | متخصصان اورولوژی</t>
+          <t>متخصصان آلرژی و ایمونولوژی | متخصصان بیهوشی | متخصصان قلب | متخصصان پرستاری بالینی | متخصصان پوست | پزشکان طب اورژانس | پزشکان خانواده | پزشکان بیمارستانی | پزشکان ناتوروپاتی | متخصصان مغز و اعصاب | پرستاران متخصص | متخصصان زنان و زایمان | چشم‌پزشکان، به‌جز کودکان | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | دستیاران پزشک | روان‌پزشکان | اورولوژیست‌ها</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0045_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0045_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال | سخن گفتن | شنیدن فعال | علوم تجربی | استراتژی‌های یادگیری | نگارش | ریاضیات</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال | سخن گفتن | گوش دادن فعال | علوم | راهبردهای یادگیری | نگارش | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | خدمات مشتریان و خدمات فردی | زیست‌شناسی | شیمی | آموزش و تدریس | ریاضیات | زبان انگلیسی | روان‌شناسی | فیزیک | رایانه و الکترونیک | مدیریت و امور اداری | حقوق و امور دولتی | ایمنی و امنیت عمومی | امور کارکنان و منابع انسانی | مهندسی و فناوری | درمان و مشاوره</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | زیست‌شناسی | شیمی | آموزش و پرورش | ریاضیات | زبان انگلیسی | روان‌شناسی | فیزیک | رایانه و الکترونیک | مدیریت و اداره | قانون و دولت | ایمنی و امنیت عمومی | پرسنل و منابع انسانی | مهندسی و فناوری | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | مرتب‌سازی اطلاعات | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | دید نزدیک | وضوح گفتار | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | روانی ایده‌ها | سرعت ادراک | سرعت نتیجه‌گیری | انعطاف‌پذیری نتیجه‌گیری | ثبات دست و بازو | مهارت کار با اعداد | استدلال ریاضی | اصالت و ابتکار | چابکی انگشتان | چابکی دستی | تقسیم توجه | تجسم فضایی | تمایز رنگ‌ها | دید دور | دقت کنترل | حفظ و به‌خاطرسپاری</t>
+          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | ترتیب‌دهی اطلاعات | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | سرعت ادراکی | سرعت بستار | انعطاف‌پذیری بستار | ثبات دست و بازو | توانایی عددی | استدلال ریاضی | اصالت | مهارت انگشتان | مهارت دستی | تقسیم توجه | تجسم | تشخیص رنگ بصری | بینایی دور | دقت کنترل | حفظ کردن</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان قلب و عروق | پرستاران بالینی متخصص | پرستاران مراقبت‌های ویژه (ICU/CCU) | تکنسین‌های فوریت‌های پزشکی (EMT) | پزشکان طب اورژانس | پزشکان متخصص بیماری‌های داخلی | بهیاران و کمک‌پرستاران دارای مجوز | ماماها | پرستاران بالینی پیشرفته (NP) | جراحان ارتوپدی (بزرگسالان) | امدادگران اورژانس (پارامدیک) | جراحان اطفال | دستیاران پزشک | کارشناسان پرستاری | متخصصان تنفس‌درمانی | دستیاران جراحی | کارشناسان اتاق عمل</t>
+          <t>پرستاران مراقبت‌های حاد | دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | پرستاران متخصص بالینی | پرستاران مراقبت‌های ویژه | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | پزشکان متخصص بیماری‌های داخلی | بهیاران و کمک‌پرستاران دارای مجوز | ماماهای پرستار | پرستاران بالینی پیشرفته | جراحان ارتوپدی، غیر از اطفال | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | جراحان اطفال | دستیاران پزشک | پرستاران | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>پرستار-ماماها (Nurse Midwives)</t>
+          <t>ماماهای پرستار (Nurse Midwives)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | یادگیری فعال | نگارش | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | روان‌شناسی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | زیست‌شناسی | جامعه‌شناسی و مردم‌شناسی | درمان و مشاوره | آموزش و تدریس | ریاضیات | حقوق و امور دولتی</t>
+          <t>پزشکی و دندان‌پزشکی | روان‌شناسی | خدمات مشتری و شخصی | زبان انگلیسی | زیست‌شناسی | جامعه‌شناسی و انسان‌شناسی | درمان و مشاوره | آموزش و پرورش | ریاضیات | قانون و دولت</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک کتبی | درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | بیان کتبی | استدلال استقرایی | دید نزدیک | تشخیص گفتار | وضوح گفتار | مرتب‌سازی اطلاعات | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | روانی ایده‌ها | ثبات دست و بازو | تقسیم توجه | سرعت ادراک | انعطاف‌پذیری نتیجه‌گیری | حفظ و به‌خاطرسپاری | چابکی انگشتان | چابکی دستی | تجسم فضایی | سرعت نتیجه‌گیری | اصالت و ابتکار</t>
+          <t>درک کتبی | درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | بیان کتبی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | ثبات دست و بازو | تقسیم توجه | سرعت ادراکی | انعطاف‌پذیری بستار | حفظ کردن | مهارت انگشتان | مهارت دستی | تجسم | سرعت بستار | اصالت</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | پرستاران بالینی پیشرفته روان‌پزشکی | متخصصان بیهوشی | پرستاران بالینی متخصص | پرستاران مراقبت‌های ویژه (ICU/CCU) | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | پزشکان مقیم بیمارستان (هسپیتالیست) | بهیاران و کمک‌پرستاران دارای مجوز | ماماها | متخصصان مغز و اعصاب (نورولوژیست) | پرستاران بیهوشی | پرستاران بالینی پیشرفته (NP) | پزشکان متخصص زنان و زایمان | امدادگران اورژانس (پارامدیک) | پزشکان متخصص کودکان | دستیاران پزشک | روان‌پزشکان | کارشناسان پرستاری</t>
+          <t>پرستاران مراقبت‌های حاد | پرستاران تخصصی روانپزشکی | متخصصان بیهوشی | پرستاران متخصص بالینی | پرستاران مراقبت‌های ویژه | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | پزشکان مقیم بیمارستان | بهیاران و کمک‌پرستاران دارای مجوز | ماماها | متخصصان مغز و اعصاب | پرستاران بیهوشی | پرستاران بالینی پیشرفته | متخصصان زنان و زایمان | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | متخصصان عمومی کودکان | دستیاران پزشک | روان‌پزشکان | پرستاران</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | علوم تجربی | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | علوم | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زبان انگلیسی | زیست‌شناسی | روان‌شناسی | خدمات مشتریان و خدمات فردی | درمان و مشاوره | آموزش و تدریس | جامعه‌شناسی و مردم‌شناسی | ریاضیات | شیمی | مدیریت و امور اداری | رایانه و الکترونیک | ایمنی و امنیت عمومی | ارتباطات و رسانه | حقوق و امور دولتی</t>
+          <t>پزشکی و دندان‌پزشکی | زبان انگلیسی | زیست‌شناسی | روان‌شناسی | خدمات مشتری و شخصی | درمان و مشاوره | آموزش و پرورش | جامعه‌شناسی و انسان‌شناسی | ریاضیات | شیمی | مدیریت و اداره | رایانه و الکترونیک | ایمنی و امنیت عمومی | ارتباطات و رسانه | قانون و دولت</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک کتبی | استدلال استقرایی | حساسیت به مسئله | بیان شفاهی | بیان کتبی | استدلال قیاسی | دید نزدیک | درک شفاهی | مرتب‌سازی اطلاعات | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری طبقه‌بندی | روانی ایده‌ها | انعطاف‌پذیری نتیجه‌گیری | سرعت نتیجه‌گیری | تمایز رنگ‌ها | دید دور | تقسیم توجه | توجه انتخابی | سرعت ادراک | حفظ و به‌خاطرسپاری | مهارت کار با اعداد | اصالت و ابتکار</t>
+          <t>درک کتبی | استدلال استقرایی | حساسیت به مسئله | بیان شفاهی | بیان کتبی | استدلال قیاسی | بینایی نزدیک | درک شفاهی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | انعطاف‌پذیری بستار | سرعت بستار | تشخیص رنگ بصری | بینایی دور | تقسیم توجه | توجه انتخابی | سرعت ادراکی | حفظ کردن | توانایی عددی | اصالت</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | پرستاران بالینی پیشرفته روان‌پزشکی | متخصصان بیهوشی | متخصصان قلب و عروق | پرستاران بالینی متخصص | پرستاران مراقبت‌های ویژه (ICU/CCU) | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | بهیاران و کمک‌پرستاران دارای مجوز | متخصصان مغز و اعصاب (نورولوژیست) | پرستاران بیهوشی | ماماها | پزشکان متخصص زنان و زایمان | امدادگران اورژانس (پارامدیک) | جراحان اطفال | پزشکان متخصص کودکان | دستیاران پزشک | روان‌پزشکان | کارشناسان پرستاری</t>
+          <t>پرستاران مراقبت‌های حاد | پرستاران تخصصی روانپزشکی | متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | پرستاران متخصص بالینی | پرستاران مراقبت‌های ویژه | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | بهیاران و کمک‌پرستاران دارای مجوز | متخصصان مغز و اعصاب | پرستاران بیهوشی | ماماهای پرستار | متخصصان زنان و زایمان | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | جراحان اطفال | متخصصان عمومی کودکان | دستیاران پزشک | روان‌پزشکان | پرستاران</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | نگارش | یادگیری فعال | نظارت | استراتژی‌های یادگیری | علوم تجربی</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | درمان و مشاوره | روان‌شناسی | پزشکی و دندانپزشکی | زبان انگلیسی | بازاریابی و فروش | رایانه و الکترونیک | زیست‌شناسی | آموزش و تدریس | امور اداری و دفتری | مدیریت و امور اداری | اقتصاد و حسابداری | امور کارکنان و منابع انسانی | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | درمان و مشاوره | روان‌شناسی | پزشکی و دندان‌پزشکی | زبان انگلیسی | فروش و بازاریابی | رایانه و الکترونیک | زیست‌شناسی | آموزش و پرورش | اداری | مدیریت و اداره | اقتصاد و حسابداری | پرسنل و منابع انسانی | ریاضیات</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | دید نزدیک | تشخیص گفتار | مرتب‌سازی اطلاعات | حساسیت شنوایی | توجه شنیداری | انعطاف‌پذیری طبقه‌بندی | سرعت ادراک | انعطاف‌پذیری نتیجه‌گیری | اصالت و ابتکار | دقت کنترل | سرعت نتیجه‌گیری | روانی ایده‌ها | چابکی انگشتان | ثبات دست و بازو</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | ترتیب‌دهی اطلاعات | حساسیت شنوایی | توجه شنیداری | انعطاف‌پذیری دسته‌بندی | سرعت ادراکی | انعطاف‌پذیری بستار | اصالت | دقت کنترل | سرعت بستار | روانی ایده‌ها | مهارت انگشتان | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>متخصصان ایمونولوژی و آلرژی | متخصصان قلب و عروق | کایروپراکتورها | متخصصان پوست و مو (درماتولوژیست) | پزشکان طب اورژانس | پزشکان متخصص بیماری‌های داخلی | متخصصان ارزیابی و تجویز سمعک | متخصصان مغز و اعصاب (نورولوژیست) | پرستاران بالینی پیشرفته (NP) | کاردرمانگران | کمک‌کاردرمانگران | متخصصان چشم‌پزشکی (بزرگسالان) | بینایی‌سنج‌ها (اپتومتریست) | جراحان ارتوپدی (بزرگسالان) | جراحان اطفال | پزشکان متخصص کودکان | پزشکان طب فیزیکی و توانبخشی | متخصصان پاتولوژی (آسیب‌شناسی) | روان‌پزشکان | گفتاردرمانگران</t>
+          <t>متخصصان آلرژی و ایمنی‌شناسی | متخصصان بیماری‌های قلب و عروق | کایروپراکتورها / متخصصان درمان دستی | متخصصان پوست و مو | پزشکان طب اورژانس | پزشکان متخصص بیماری‌های داخلی | کارشناسان تجویز و ساخت سمعک | متخصصان مغز و اعصاب | پرستاران بالینی پیشرفته | کاردرمانگران | کمک‌یاران کاردرمانی | متخصصان چشم‌پزشکی، غیر از اطفال | بینایی‌سنج‌ها (اپتومتریست‌ها) | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | پزشکان متخصص پاتولوژی | روان‌پزشکان | آسیب‌شناسان گفتار و زبان / گفتاردرمانگران</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | نظارت | علوم تجربی | نگارش | درک مطلب | سخن گفتن | یادگیری فعال | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>تفکر انتقادی | گوش دادن فعال | نظارت | علوم | نگارش | درک مطلب | سخن گفتن | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | زبان انگلیسی | شیمی | خدمات مشتریان و خدمات فردی | روان‌شناسی | فیزیک | ریاضیات | آموزش و تدریس | مدیریت و امور اداری</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | زبان انگلیسی | شیمی | خدمات مشتری و شخصی | روان‌شناسی | فیزیک | ریاضیات | آموزش و پرورش | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | استدلال قیاسی | درک شفاهی | استدلال استقرایی | درک کتبی | دید نزدیک | بیان شفاهی | بیان کتبی | مرتب‌سازی اطلاعات | توجه انتخابی | انعطاف‌پذیری نتیجه‌گیری | سرعت ادراک | ثبات دست و بازو | تشخیص گفتار | وضوح گفتار | چابکی انگشتان | روانی ایده‌ها | دقت کنترل | چابکی دستی | تقسیم توجه | دید دور | جهت‌یابی پاسخ | مهارت کار با اعداد | استدلال ریاضی | انعطاف‌پذیری طبقه‌بندی</t>
+          <t>حساسیت به مسئله | استدلال قیاسی | درک شفاهی | استدلال استقرایی | درک کتبی | بینایی نزدیک | بیان شفاهی | بیان کتبی | ترتیب‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری بستار | سرعت ادراکی | ثبات دست و بازو | تشخیص گفتار | وضوح گفتار | مهارت انگشتان | روانی ایده‌ها | دقت کنترل | مهارت دستی | تقسیم توجه | بینایی دور | جهت‌گیری پاسخ | توانایی عددی | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | دستیاران متخصص بیهوشی | متخصصان قلب و عروق | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | متخصصان مغز و اعصاب (نورولوژیست) | پرستاران بیهوشی | پرستاران بالینی پیشرفته (NP) | پزشکان متخصص زنان و زایمان | متخصصان چشم‌پزشکی (بزرگسالان) | جراحان ارتوپدی (بزرگسالان) | امدادگران اورژانس (پارامدیک) | جراحان اطفال | پزشکان طب فیزیکی و توانبخشی | دستیاران پزشک | کارشناسان پرستاری | متخصصان تنفس‌درمانی | دستیاران جراحی | متخصصان اورولوژی</t>
+          <t>پرستاران مراقبت‌های حاد | دستیاران متخصص بیهوشی | متخصصان بیماری‌های قلب و عروق | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | متخصصان مغز و اعصاب | پرستاران بیهوشی | پرستاران بالینی پیشرفته | متخصصان زنان و زایمان | متخصصان چشم‌پزشکی، غیر از اطفال | جراحان ارتوپدی، غیر از اطفال | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | جراحان اطفال | متخصصان طب فیزیکی و توانبخشی | دستیاران پزشک | پرستاران | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران | دستیاران جراحی | متخصصان اورولوژی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,22 +788,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Epic Systems | MEDITECH software | نرم‌افزار مانیتورینگ Watchman Monitoring</t>
+          <t>Epic Systems | نرم‌افزار MEDITECH | نرم‌افزار مانیتورینگ Watchman Monitoring</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | علوم تجربی | نظارت | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | شیمی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | روان‌شناسی | آموزش و تدریس | فیزیک | مدیریت و امور اداری | درمان و مشاوره</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | شیمی | خدمات مشتری و شخصی | زبان انگلیسی | روان‌شناسی | آموزش و پرورش | فیزیک | مدیریت و اداره | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | وضوح گفتار | تشخیص گفتار | چابکی انگشتان | ثبات دست و بازو | چابکی دستی | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | تجسم فضایی | تقسیم توجه | دقت کنترل | ادراک عمق</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | ثبات دست و بازو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | تقسیم توجه | دقت کنترل | درک عمق</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | متخصصان ایمونولوژی و آلرژی | دستیاران متخصص بیهوشی | متخصصان بیهوشی | تکنسین‌ها و کارشناسان قلب و عروق | متخصصان پوست و مو (درماتولوژیست) | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | متخصصان مغز و اعصاب (نورولوژیست) | پرستاران بالینی پیشرفته (NP) | پزشکان متخصص زنان و زایمان | متخصصان چشم‌پزشکی (بزرگسالان) | جراحان ارتوپدی (بزرگسالان) | جراحان اطفال | پزشکان متخصص کودکان | پزشکان طب فیزیکی و توانبخشی | دستیاران پزشک | متخصصان رادیولوژی | متخصصان اورولوژی</t>
+          <t>پرستاران مراقبت‌های حاد | متخصصان آلرژی و ایمنی‌شناسی | دستیاران متخصص بیهوشی | متخصصان بیهوشی | کارشناسان و تکنسین‌های قلب و عروق | متخصصان پوست و مو | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | متخصصان مغز و اعصاب | پرستاران بالینی پیشرفته | متخصصان زنان و زایمان | متخصصان چشم‌پزشکی، غیر از اطفال | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | دستیاران پزشک | متخصصان رادیولوژی | متخصصان اورولوژی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | درک مطلب | سخن گفتن | یادگیری فعال | علوم تجربی | نگارش | نظارت | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن | یادگیری فعال | علوم | نگارش | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | مدیریت و امور اداری | آموزش و تدریس | زیست‌شناسی | امور کارکنان و منابع انسانی | روان‌شناسی | رایانه و الکترونیک</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | زبان انگلیسی | مدیریت و اداره | آموزش و پرورش | زیست‌شناسی | پرسنل و منابع انسانی | روان‌شناسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | درک کتبی | دید نزدیک | بیان کتبی | مرتب‌سازی اطلاعات | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری طبقه‌بندی | انعطاف‌پذیری نتیجه‌گیری | تمایز رنگ‌ها | توجه انتخابی | دید دور | چابکی انگشتان | ثبات دست و بازو | سرعت ادراک | حفظ و به‌خاطرسپاری | اصالت و ابتکار | روانی ایده‌ها</t>
+          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | درک کتبی | بینایی نزدیک | بیان کتبی | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | تشخیص رنگ بصری | توجه انتخابی | بینایی دور | مهارت انگشتان | ثبات دست و بازو | سرعت ادراکی | حفظ کردن | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>متخصصان ایمونولوژی و آلرژی | متخصصان بیهوشی | متخصصان قلب و عروق | کایروپراکتورها | پزشکان طب اورژانس | پزشکان متخصص بیماری‌های داخلی | پزشکان طب طبیعی (نتروپاتی) | متخصصان مغز و اعصاب (نورولوژیست) | پرستاران بالینی پیشرفته (NP) | پزشکان متخصص زنان و زایمان | متخصصان چشم‌پزشکی (بزرگسالان) | بینایی‌سنج‌ها (اپتومتریست) | جراحان دهان، فک و صورت | جراحان ارتوپدی (بزرگسالان) | جراحان اطفال | پزشکان متخصص کودکان | پزشکان طب فیزیکی و توانبخشی | دستیاران پزشک | متخصصان طب پا (پودیاتریست) | متخصصان اورولوژی</t>
+          <t>متخصصان آلرژی و ایمنی‌شناسی | متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | کایروپراکتورها / متخصصان درمان دستی | پزشکان طب اورژانس | پزشکان متخصص بیماری‌های داخلی | پزشکان طب طبیعی و نتوپاتی | متخصصان مغز و اعصاب | پرستاران بالینی پیشرفته | متخصصان زنان و زایمان | متخصصان چشم‌پزشکی، غیر از اطفال | بینایی‌سنج‌ها (اپتومتریست‌ها) | جراحان دهان، فک و صورت | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | دستیاران پزشک | پزشکان متخصص پا و مچ پا | متخصصان اورولوژی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,22 +902,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Epic Systems | MEDITECH software</t>
+          <t>Epic Systems | نرم‌افزار MEDITECH</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | نظارت | نگارش | یادگیری فعال | استراتژی‌های یادگیری | علوم تجربی</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زبان انگلیسی | زیست‌شناسی | روان‌شناسی | درمان و مشاوره | خدمات مشتریان و خدمات فردی | آموزش و تدریس | ایمنی و امنیت عمومی | شیمی | ریاضیات</t>
+          <t>پزشکی و دندان‌پزشکی | زبان انگلیسی | زیست‌شناسی | روان‌شناسی | درمان و مشاوره | خدمات مشتری و شخصی | آموزش و پرورش | ایمنی و امنیت عمومی | شیمی | ریاضیات</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | مرتب‌سازی اطلاعات | دید نزدیک | انعطاف‌پذیری نتیجه‌گیری | روانی ایده‌ها | توجه انتخابی | اصالت و ابتکار | انعطاف‌پذیری طبقه‌بندی | سرعت نتیجه‌گیری | ثبات دست و بازو | سرعت ادراک | حفظ و به‌خاطرسپاری | چابکی انگشتان | دید دور | چابکی دستی | تقسیم توجه | تمایز رنگ‌ها | سرعت حرکات مچ و انگشتان | هماهنگی اندام‌ها</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | ترتیب‌دهی اطلاعات | بینایی نزدیک | انعطاف‌پذیری بستار | روانی ایده‌ها | توجه انتخابی | اصالت | انعطاف‌پذیری دسته‌بندی | سرعت بستار | ثبات دست و بازو | سرعت ادراکی | حفظ کردن | مهارت انگشتان | بینایی دور | مهارت دستی | تقسیم توجه | تشخیص رنگ بصری | سرعت مچ و انگشتان | هماهنگی چند عضو</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | متخصصان بیهوشی | متخصصان قلب و عروق | پرستاران بالینی متخصص | پرستاران مراقبت‌های ویژه (ICU/CCU) | تکنسین‌های فوریت‌های پزشکی (EMT) | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | پزشکان مقیم بیمارستان (هسپیتالیست) | متخصصان مغز و اعصاب (نورولوژیست) | پرستاران بالینی پیشرفته (NP) | پزشکان متخصص زنان و زایمان | جراحان ارتوپدی (بزرگسالان) | امدادگران اورژانس (پارامدیک) | جراحان اطفال | پزشکان متخصص کودکان | پزشکان طب فیزیکی و توانبخشی | دستیاران پزشک | روان‌پزشکان | کارشناسان پرستاری</t>
+          <t>پرستاران مراقبت‌های حاد | متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | پرستاران متخصص بالینی | پرستاران مراقبت‌های ویژه | تکنسین‌های فوریت‌های پزشکی | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | پزشکان مقیم بیمارستان | متخصصان مغز و اعصاب | پرستاران بالینی پیشرفته | متخصصان زنان و زایمان | جراحان ارتوپدی، غیر از اطفال | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | جراحان اطفال | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | دستیاران پزشک | روان‌پزشکان | پرستاران</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | درک مطلب | سخن گفتن | نگارش | نظارت | یادگیری فعال | علوم تجربی | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن | نگارش | نظارت | یادگیری فعال | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زبان انگلیسی | درمان و مشاوره | روان‌شناسی | زیست‌شناسی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | ریاضیات | آموزش و تدریس | جامعه‌شناسی و مردم‌شناسی | حقوق و امور دولتی</t>
+          <t>پزشکی و دندان‌پزشکی | زبان انگلیسی | درمان و مشاوره | روان‌شناسی | زیست‌شناسی | خدمات مشتری و شخصی | رایانه و الکترونیک | ریاضیات | آموزش و پرورش | جامعه‌شناسی و انسان‌شناسی | قانون و دولت</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | بیان شفاهی | استدلال قیاسی | درک کتبی | استدلال استقرایی | بیان کتبی | وضوح گفتار | دید نزدیک | تشخیص گفتار | انعطاف‌پذیری نتیجه‌گیری | توجه انتخابی | مرتب‌سازی اطلاعات | روانی ایده‌ها | تقسیم توجه | سرعت ادراک | انعطاف‌پذیری طبقه‌بندی | اصالت و ابتکار</t>
+          <t>حساسیت به مسئله | درک شفاهی | بیان شفاهی | استدلال قیاسی | درک کتبی | استدلال استقرایی | بیان کتبی | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | انعطاف‌پذیری بستار | توجه انتخابی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | تقسیم توجه | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | اصالت</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>پرستاران بالینی پیشرفته روان‌پزشکی | متخصصان بیهوشی | متخصصان قلب و عروق | پرستاران بالینی متخصص | پزشکان طب اورژانس | پزشکان متخصص بیماری‌های داخلی | پزشکان مقیم بیمارستان (هسپیتالیست) | پزشکان طب طبیعی (نتروپاتی) | متخصصان مغز و اعصاب (نورولوژیست) | ماماها | پرستاران بالینی پیشرفته (NP) | پزشکان متخصص زنان و زایمان | جراحان ارتوپدی (بزرگسالان) | جراحان اطفال | پزشکان متخصص کودکان | پزشکان طب فیزیکی و توانبخشی | دستیاران پزشک | متخصصان طب پیشگیری | روان‌پزشکان | کارشناسان پرستاری</t>
+          <t>پرستاران تخصصی روانپزشکی | متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | پرستاران متخصص بالینی | پزشکان طب اورژانس | پزشکان متخصص بیماری‌های داخلی | پزشکان مقیم بیمارستان | پزشکان طب طبیعی و نتوپاتی | متخصصان مغز و اعصاب | ماماهای پرستار | پرستاران بالینی پیشرفته | متخصصان زنان و زایمان | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | دستیاران پزشک | متخصصان پزشکی اجتماعی و طب پیشگیری | روان‌پزشکان | پرستاران</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | نگارش | تفکر انتقادی | علوم تجربی | سخن گفتن | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | علوم | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | درمان و مشاوره | روان‌شناسی | آموزش و تدریس | زبان انگلیسی | مدیریت و امور اداری | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | ریاضیات | شیمی | امور کارکنان و منابع انسانی | ایمنی و امنیت عمومی | امور اداری و دفتری | اقتصاد و حسابداری</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | درمان و مشاوره | روان‌شناسی | آموزش و پرورش | زبان انگلیسی | مدیریت و اداره | رایانه و الکترونیک | خدمات مشتری و شخصی | ریاضیات | شیمی | پرسنل و منابع انسانی | ایمنی و امنیت عمومی | اداری | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | استدلال استقرایی | بیان شفاهی | درک کتبی | استدلال قیاسی | بیان کتبی | مرتب‌سازی اطلاعات | انعطاف‌پذیری طبقه‌بندی | دید نزدیک | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری نتیجه‌گیری | سرعت ادراک | توجه انتخابی | روانی ایده‌ها | دید دور | حفظ و به‌خاطرسپاری | مهارت کار با اعداد | استدلال ریاضی | اصالت و ابتکار</t>
+          <t>حساسیت به مسئله | درک شفاهی | استدلال استقرایی | بیان شفاهی | درک کتبی | استدلال قیاسی | بیان کتبی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری بستار | سرعت ادراکی | توجه انتخابی | روانی ایده‌ها | بینایی دور | حفظ کردن | توانایی عددی | استدلال ریاضی | اصالت</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>متخصصان ایمونولوژی و آلرژی | متخصصان بیهوشی | متخصصان قلب و عروق | پرستاران بالینی متخصص | متخصصان پوست و مو (درماتولوژیست) | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان مقیم بیمارستان (هسپیتالیست) | پزشکان طب طبیعی (نتروپاتی) | متخصصان مغز و اعصاب (نورولوژیست) | پرستاران بالینی پیشرفته (NP) | پزشکان متخصص زنان و زایمان | متخصصان چشم‌پزشکی (بزرگسالان) | جراحان ارتوپدی (بزرگسالان) | جراحان اطفال | پزشکان متخصص کودکان | پزشکان طب فیزیکی و توانبخشی | دستیاران پزشک | روان‌پزشکان | متخصصان اورولوژی</t>
+          <t>متخصصان آلرژی و ایمنی‌شناسی | متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | پرستاران متخصص بالینی | متخصصان پوست و مو | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان مقیم بیمارستان | پزشکان طب طبیعی و نتوپاتی | متخصصان مغز و اعصاب | پرستاران بالینی پیشرفته | متخصصان زنان و زایمان | متخصصان چشم‌پزشکی، غیر از اطفال | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | دستیاران پزشک | روان‌پزشکان | متخصصان اورولوژی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
